--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134134751</v>
       </c>
       <c r="B2" t="n">
-        <v>99191</v>
+        <v>99201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134134729</v>
       </c>
       <c r="B3" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>134134745</v>
       </c>
       <c r="B4" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>134134894</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>134134765</v>
       </c>
       <c r="B6" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134791</v>
+        <v>134134747</v>
       </c>
       <c r="B7" t="n">
-        <v>99197</v>
+        <v>99201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R7" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,6 +1279,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134747</v>
+        <v>134134791</v>
       </c>
       <c r="B8" t="n">
-        <v>99191</v>
+        <v>99207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R8" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1390,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
         <v>134134792</v>
       </c>
       <c r="B9" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,27 +1533,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134789</v>
+        <v>134134780</v>
       </c>
       <c r="B10" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,17 +1561,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716826</v>
+        <v>716862</v>
       </c>
       <c r="R10" t="n">
-        <v>6368340</v>
+        <v>6368351</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1613,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,27 +1644,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134780</v>
+        <v>134134789</v>
       </c>
       <c r="B11" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,26 +1672,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716862</v>
+        <v>716826</v>
       </c>
       <c r="R11" t="n">
-        <v>6368351</v>
+        <v>6368340</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,7 +1754,7 @@
         <v>134134748</v>
       </c>
       <c r="B12" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>134134755</v>
       </c>
       <c r="B13" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>134134743</v>
       </c>
       <c r="B14" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>134134782</v>
       </c>
       <c r="B15" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>134134753</v>
       </c>
       <c r="B16" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134134775</v>
+        <v>134134778</v>
       </c>
       <c r="B17" t="n">
-        <v>99197</v>
+        <v>99207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716872</v>
+        <v>716866</v>
       </c>
       <c r="R17" t="n">
-        <v>6368325</v>
+        <v>6368338</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,27 +2372,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134134778</v>
+        <v>134134767</v>
       </c>
       <c r="B18" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2400,26 +2400,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716866</v>
+        <v>716880</v>
       </c>
       <c r="R18" t="n">
-        <v>6368338</v>
+        <v>6368316</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,27 +2474,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134134767</v>
+        <v>134134775</v>
       </c>
       <c r="B19" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2511,17 +2502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716880</v>
+        <v>716872</v>
       </c>
       <c r="R19" t="n">
-        <v>6368316</v>
+        <v>6368325</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2588,7 +2588,7 @@
         <v>134134795</v>
       </c>
       <c r="B20" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>134134761</v>
       </c>
       <c r="B21" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>134134740</v>
       </c>
       <c r="B22" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,27 +2896,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134794</v>
+        <v>134134786</v>
       </c>
       <c r="B23" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,29 +2924,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716821</v>
+        <v>716848</v>
       </c>
       <c r="R23" t="n">
-        <v>6368327</v>
+        <v>6368363</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2978,6 +2969,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2989,7 +2985,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3007,27 +3003,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B24" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3035,20 +3031,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R24" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,11 +3085,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
         <v>134134763</v>
       </c>
       <c r="B25" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>134134727</v>
       </c>
       <c r="B26" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>134134776</v>
       </c>
       <c r="B27" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>134134893</v>
       </c>
       <c r="B28" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>134134773</v>
       </c>
       <c r="B29" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,27 +3629,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134769</v>
+        <v>134134742</v>
       </c>
       <c r="B30" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3657,17 +3657,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716876</v>
+        <v>716930</v>
       </c>
       <c r="R30" t="n">
-        <v>6368320</v>
+        <v>6368372</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3731,27 +3740,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134742</v>
+        <v>134134769</v>
       </c>
       <c r="B31" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3759,26 +3768,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716930</v>
+        <v>716876</v>
       </c>
       <c r="R31" t="n">
-        <v>6368372</v>
+        <v>6368320</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134747</v>
+        <v>134134791</v>
       </c>
       <c r="B7" t="n">
-        <v>99201</v>
+        <v>99207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R7" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1310,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134791</v>
+        <v>134134792</v>
       </c>
       <c r="B8" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1343,16 +1338,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
@@ -1395,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>AVA slut 20 m V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,45 +1417,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134792</v>
+        <v>134134747</v>
       </c>
       <c r="B9" t="n">
-        <v>110141</v>
+        <v>99201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R9" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>AVA slut 20 m V.</t>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2261,7 +2261,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134134778</v>
+        <v>134134775</v>
       </c>
       <c r="B17" t="n">
         <v>99207</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716866</v>
+        <v>716872</v>
       </c>
       <c r="R17" t="n">
-        <v>6368338</v>
+        <v>6368325</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,27 +2372,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134134767</v>
+        <v>134134778</v>
       </c>
       <c r="B18" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2400,17 +2400,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716880</v>
+        <v>716866</v>
       </c>
       <c r="R18" t="n">
-        <v>6368316</v>
+        <v>6368338</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2474,27 +2483,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134134775</v>
+        <v>134134767</v>
       </c>
       <c r="B19" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2502,26 +2511,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716872</v>
+        <v>716880</v>
       </c>
       <c r="R19" t="n">
-        <v>6368325</v>
+        <v>6368316</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2896,27 +2896,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B23" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,20 +2924,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R23" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2969,11 +2978,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2985,7 +2989,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3003,27 +3007,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134794</v>
+        <v>134134786</v>
       </c>
       <c r="B24" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3031,29 +3035,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716821</v>
+        <v>716848</v>
       </c>
       <c r="R24" t="n">
-        <v>6368327</v>
+        <v>6368363</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3085,6 +3080,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134727</v>
+        <v>134134893</v>
       </c>
       <c r="B26" t="n">
-        <v>110141</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716881</v>
+        <v>716917</v>
       </c>
       <c r="R26" t="n">
-        <v>6368310</v>
+        <v>6368326</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3289,6 +3294,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3297,11 +3307,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3318,7 +3323,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134776</v>
+        <v>134134727</v>
       </c>
       <c r="B27" t="n">
         <v>110141</v>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716866</v>
+        <v>716881</v>
       </c>
       <c r="R27" t="n">
-        <v>6368338</v>
+        <v>6368310</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3420,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134893</v>
+        <v>134134776</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>110141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,39 +3436,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716917</v>
+        <v>716866</v>
       </c>
       <c r="R28" t="n">
-        <v>6368326</v>
+        <v>6368338</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3498,11 +3498,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3511,6 +3506,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3629,27 +3629,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134742</v>
+        <v>134134769</v>
       </c>
       <c r="B30" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3657,26 +3657,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716930</v>
+        <v>716876</v>
       </c>
       <c r="R30" t="n">
-        <v>6368372</v>
+        <v>6368320</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3740,27 +3731,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134769</v>
+        <v>134134742</v>
       </c>
       <c r="B31" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3768,17 +3759,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716876</v>
+        <v>716930</v>
       </c>
       <c r="R31" t="n">
-        <v>6368320</v>
+        <v>6368372</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>134134729</v>
       </c>
       <c r="B3" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>134134745</v>
       </c>
       <c r="B4" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>134134765</v>
       </c>
       <c r="B6" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134791</v>
+        <v>134134747</v>
       </c>
       <c r="B7" t="n">
-        <v>99207</v>
+        <v>99201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R7" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,6 +1279,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,7 +1318,7 @@
         <v>134134792</v>
       </c>
       <c r="B8" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134747</v>
+        <v>134134791</v>
       </c>
       <c r="B9" t="n">
-        <v>99201</v>
+        <v>99207</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R9" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1497,11 +1502,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,27 +1533,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134780</v>
+        <v>134134789</v>
       </c>
       <c r="B10" t="n">
-        <v>99207</v>
+        <v>110142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,26 +1561,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716862</v>
+        <v>716826</v>
       </c>
       <c r="R10" t="n">
-        <v>6368351</v>
+        <v>6368340</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1613,6 +1604,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,27 +1640,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134789</v>
+        <v>134134780</v>
       </c>
       <c r="B11" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1672,17 +1668,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716826</v>
+        <v>716862</v>
       </c>
       <c r="R11" t="n">
-        <v>6368340</v>
+        <v>6368351</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1715,11 +1720,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,7 +1754,7 @@
         <v>134134748</v>
       </c>
       <c r="B12" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>134134755</v>
       </c>
       <c r="B13" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>134134743</v>
       </c>
       <c r="B14" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>134134782</v>
       </c>
       <c r="B15" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>134134753</v>
       </c>
       <c r="B16" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>134134767</v>
       </c>
       <c r="B19" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>134134795</v>
       </c>
       <c r="B20" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>134134761</v>
       </c>
       <c r="B21" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>134134740</v>
       </c>
       <c r="B22" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,27 +2896,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134794</v>
+        <v>134134786</v>
       </c>
       <c r="B23" t="n">
-        <v>99207</v>
+        <v>110142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,29 +2924,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716821</v>
+        <v>716848</v>
       </c>
       <c r="R23" t="n">
-        <v>6368327</v>
+        <v>6368363</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2978,6 +2969,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2989,7 +2985,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3007,27 +3003,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B24" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3035,20 +3031,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R24" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,11 +3085,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
         <v>134134763</v>
       </c>
       <c r="B25" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>134134727</v>
       </c>
       <c r="B27" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>134134776</v>
       </c>
       <c r="B28" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>134134773</v>
       </c>
       <c r="B29" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>134134769</v>
       </c>
       <c r="B30" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -3216,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134893</v>
+        <v>134134727</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>110142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,39 +3227,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716917</v>
+        <v>716881</v>
       </c>
       <c r="R26" t="n">
-        <v>6368326</v>
+        <v>6368310</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3294,11 +3289,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3307,6 +3297,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3323,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134727</v>
+        <v>134134893</v>
       </c>
       <c r="B27" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3334,34 +3329,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716881</v>
+        <v>716917</v>
       </c>
       <c r="R27" t="n">
-        <v>6368310</v>
+        <v>6368326</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3396,6 +3396,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3404,11 +3409,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -3216,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134727</v>
+        <v>134134893</v>
       </c>
       <c r="B26" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716881</v>
+        <v>716917</v>
       </c>
       <c r="R26" t="n">
-        <v>6368310</v>
+        <v>6368326</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3289,6 +3294,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3297,11 +3307,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3318,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134893</v>
+        <v>134134727</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>110142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,39 +3334,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716917</v>
+        <v>716881</v>
       </c>
       <c r="R27" t="n">
-        <v>6368326</v>
+        <v>6368310</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3396,11 +3396,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3409,6 +3404,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134134751</v>
       </c>
       <c r="B2" t="n">
-        <v>99201</v>
+        <v>99203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134134729</v>
       </c>
       <c r="B3" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>134134745</v>
       </c>
       <c r="B4" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>134134765</v>
       </c>
       <c r="B6" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134747</v>
+        <v>134134791</v>
       </c>
       <c r="B7" t="n">
-        <v>99201</v>
+        <v>99209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R7" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,7 +1313,7 @@
         <v>134134792</v>
       </c>
       <c r="B8" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134791</v>
+        <v>134134747</v>
       </c>
       <c r="B9" t="n">
-        <v>99207</v>
+        <v>99203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1466,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R9" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1502,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134789</v>
+        <v>134134748</v>
       </c>
       <c r="B10" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716826</v>
+        <v>716919</v>
       </c>
       <c r="R10" t="n">
-        <v>6368340</v>
+        <v>6368359</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,27 +1635,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134780</v>
+        <v>134134789</v>
       </c>
       <c r="B11" t="n">
-        <v>99207</v>
+        <v>110144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,26 +1663,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716862</v>
+        <v>716826</v>
       </c>
       <c r="R11" t="n">
-        <v>6368351</v>
+        <v>6368340</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,6 +1706,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,27 +1742,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134134748</v>
+        <v>134134780</v>
       </c>
       <c r="B12" t="n">
-        <v>110142</v>
+        <v>99209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1779,17 +1770,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716919</v>
+        <v>716862</v>
       </c>
       <c r="R12" t="n">
-        <v>6368359</v>
+        <v>6368351</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1856,7 @@
         <v>134134755</v>
       </c>
       <c r="B13" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134134743</v>
+        <v>134134753</v>
       </c>
       <c r="B14" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716930</v>
+        <v>716919</v>
       </c>
       <c r="R14" t="n">
-        <v>6368372</v>
+        <v>6368337</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134134782</v>
+        <v>134134743</v>
       </c>
       <c r="B15" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716867</v>
+        <v>716930</v>
       </c>
       <c r="R15" t="n">
-        <v>6368358</v>
+        <v>6368372</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134134753</v>
+        <v>134134782</v>
       </c>
       <c r="B16" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716919</v>
+        <v>716867</v>
       </c>
       <c r="R16" t="n">
-        <v>6368337</v>
+        <v>6368358</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134134775</v>
+        <v>134134778</v>
       </c>
       <c r="B17" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716872</v>
+        <v>716866</v>
       </c>
       <c r="R17" t="n">
-        <v>6368325</v>
+        <v>6368338</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,27 +2372,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134134778</v>
+        <v>134134767</v>
       </c>
       <c r="B18" t="n">
-        <v>99207</v>
+        <v>110144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2400,26 +2400,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716866</v>
+        <v>716880</v>
       </c>
       <c r="R18" t="n">
-        <v>6368338</v>
+        <v>6368316</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,27 +2474,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134134767</v>
+        <v>134134775</v>
       </c>
       <c r="B19" t="n">
-        <v>110142</v>
+        <v>99209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2511,17 +2502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716880</v>
+        <v>716872</v>
       </c>
       <c r="R19" t="n">
-        <v>6368316</v>
+        <v>6368325</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134134795</v>
+        <v>134134761</v>
       </c>
       <c r="B20" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716821</v>
+        <v>716908</v>
       </c>
       <c r="R20" t="n">
-        <v>6368327</v>
+        <v>6368321</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134134761</v>
+        <v>134134795</v>
       </c>
       <c r="B21" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716908</v>
+        <v>716821</v>
       </c>
       <c r="R21" t="n">
-        <v>6368321</v>
+        <v>6368327</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,7 +2792,7 @@
         <v>134134740</v>
       </c>
       <c r="B22" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,27 +2896,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B23" t="n">
-        <v>110142</v>
+        <v>99209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,20 +2924,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R23" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2969,11 +2978,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2985,7 +2989,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3003,27 +3007,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134794</v>
+        <v>134134786</v>
       </c>
       <c r="B24" t="n">
-        <v>99207</v>
+        <v>110144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3031,29 +3035,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716821</v>
+        <v>716848</v>
       </c>
       <c r="R24" t="n">
-        <v>6368327</v>
+        <v>6368363</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3085,6 +3080,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
         <v>134134763</v>
       </c>
       <c r="B25" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>134134727</v>
       </c>
       <c r="B26" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134893</v>
+        <v>134134776</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>110144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,39 +3329,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716917</v>
+        <v>716866</v>
       </c>
       <c r="R27" t="n">
-        <v>6368326</v>
+        <v>6368338</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3396,11 +3391,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3409,6 +3399,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3425,10 +3420,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134776</v>
+        <v>134134893</v>
       </c>
       <c r="B28" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3436,34 +3431,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716866</v>
+        <v>716917</v>
       </c>
       <c r="R28" t="n">
-        <v>6368338</v>
+        <v>6368326</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3498,6 +3498,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3506,11 +3511,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3530,7 +3530,7 @@
         <v>134134773</v>
       </c>
       <c r="B29" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,27 +3629,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134769</v>
+        <v>134134742</v>
       </c>
       <c r="B30" t="n">
-        <v>110142</v>
+        <v>99209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3657,17 +3657,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716876</v>
+        <v>716930</v>
       </c>
       <c r="R30" t="n">
-        <v>6368320</v>
+        <v>6368372</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3731,27 +3740,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134742</v>
+        <v>134134769</v>
       </c>
       <c r="B31" t="n">
-        <v>99207</v>
+        <v>110144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3759,26 +3768,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716930</v>
+        <v>716876</v>
       </c>
       <c r="R31" t="n">
-        <v>6368372</v>
+        <v>6368320</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134791</v>
+        <v>134134747</v>
       </c>
       <c r="B7" t="n">
-        <v>99210</v>
+        <v>99204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R7" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,6 +1279,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,27 +1315,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134792</v>
+        <v>134134791</v>
       </c>
       <c r="B8" t="n">
-        <v>110145</v>
+        <v>99210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1338,7 +1343,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
@@ -1381,11 +1395,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>AVA slut 20 m V.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,54 +1426,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134747</v>
+        <v>134134792</v>
       </c>
       <c r="B9" t="n">
-        <v>99204</v>
+        <v>110145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R9" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Även 5 fjolårsstänglar.</t>
+          <t>AVA slut 20 m V.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134789</v>
+        <v>134134748</v>
       </c>
       <c r="B10" t="n">
         <v>110145</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716826</v>
+        <v>716919</v>
       </c>
       <c r="R10" t="n">
-        <v>6368340</v>
+        <v>6368359</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1604,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,27 +1635,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134780</v>
+        <v>134134789</v>
       </c>
       <c r="B11" t="n">
-        <v>99210</v>
+        <v>110145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1668,26 +1663,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716862</v>
+        <v>716826</v>
       </c>
       <c r="R11" t="n">
-        <v>6368351</v>
+        <v>6368340</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,6 +1706,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1751,27 +1742,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134134748</v>
+        <v>134134780</v>
       </c>
       <c r="B12" t="n">
-        <v>110145</v>
+        <v>99210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1779,17 +1770,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716919</v>
+        <v>716862</v>
       </c>
       <c r="R12" t="n">
-        <v>6368359</v>
+        <v>6368351</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134893</v>
+        <v>134134727</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>110145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,39 +3227,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716917</v>
+        <v>716881</v>
       </c>
       <c r="R26" t="n">
-        <v>6368326</v>
+        <v>6368310</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3294,11 +3289,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3307,6 +3297,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3323,7 +3318,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134727</v>
+        <v>134134776</v>
       </c>
       <c r="B27" t="n">
         <v>110145</v>
@@ -3358,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716881</v>
+        <v>716866</v>
       </c>
       <c r="R27" t="n">
-        <v>6368310</v>
+        <v>6368338</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3425,10 +3420,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134776</v>
+        <v>134134893</v>
       </c>
       <c r="B28" t="n">
-        <v>110145</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3436,34 +3431,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716866</v>
+        <v>716917</v>
       </c>
       <c r="R28" t="n">
-        <v>6368338</v>
+        <v>6368326</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3498,6 +3498,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3506,11 +3511,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134134751</v>
       </c>
       <c r="B2" t="n">
-        <v>99204</v>
+        <v>99211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>134134729</v>
       </c>
       <c r="B3" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>134134745</v>
       </c>
       <c r="B4" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>134134765</v>
       </c>
       <c r="B6" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134747</v>
+        <v>134134791</v>
       </c>
       <c r="B7" t="n">
-        <v>99204</v>
+        <v>99217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716928</v>
+        <v>716813</v>
       </c>
       <c r="R7" t="n">
-        <v>6368363</v>
+        <v>6368335</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134791</v>
+        <v>134134747</v>
       </c>
       <c r="B8" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1359,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716813</v>
+        <v>716928</v>
       </c>
       <c r="R8" t="n">
-        <v>6368335</v>
+        <v>6368363</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1395,6 +1390,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1429,7 @@
         <v>134134792</v>
       </c>
       <c r="B9" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>134134748</v>
       </c>
       <c r="B10" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,27 +1635,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134789</v>
+        <v>134134780</v>
       </c>
       <c r="B11" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1663,17 +1663,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716826</v>
+        <v>716862</v>
       </c>
       <c r="R11" t="n">
-        <v>6368340</v>
+        <v>6368351</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1706,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,27 +1746,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134134780</v>
+        <v>134134789</v>
       </c>
       <c r="B12" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1770,26 +1774,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716862</v>
+        <v>716826</v>
       </c>
       <c r="R12" t="n">
-        <v>6368351</v>
+        <v>6368340</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1822,6 +1817,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1856,7 @@
         <v>134134755</v>
       </c>
       <c r="B13" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>134134743</v>
       </c>
       <c r="B14" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>134134782</v>
       </c>
       <c r="B15" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>134134753</v>
       </c>
       <c r="B16" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>134134775</v>
       </c>
       <c r="B17" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>134134778</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>134134767</v>
       </c>
       <c r="B19" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134134795</v>
+        <v>134134761</v>
       </c>
       <c r="B20" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716821</v>
+        <v>716908</v>
       </c>
       <c r="R20" t="n">
-        <v>6368327</v>
+        <v>6368321</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134134761</v>
+        <v>134134795</v>
       </c>
       <c r="B21" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716908</v>
+        <v>716821</v>
       </c>
       <c r="R21" t="n">
-        <v>6368321</v>
+        <v>6368327</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2792,7 +2792,7 @@
         <v>134134740</v>
       </c>
       <c r="B22" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,27 +2896,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B23" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,20 +2924,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R23" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2969,11 +2978,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2985,7 +2989,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3003,27 +3007,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134794</v>
+        <v>134134786</v>
       </c>
       <c r="B24" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3031,29 +3035,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716821</v>
+        <v>716848</v>
       </c>
       <c r="R24" t="n">
-        <v>6368327</v>
+        <v>6368363</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3085,6 +3080,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
         <v>134134763</v>
       </c>
       <c r="B25" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134727</v>
+        <v>134134893</v>
       </c>
       <c r="B26" t="n">
-        <v>110145</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716881</v>
+        <v>716917</v>
       </c>
       <c r="R26" t="n">
-        <v>6368310</v>
+        <v>6368326</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3289,6 +3294,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3297,11 +3307,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3318,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134776</v>
+        <v>134134727</v>
       </c>
       <c r="B27" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716866</v>
+        <v>716881</v>
       </c>
       <c r="R27" t="n">
-        <v>6368338</v>
+        <v>6368310</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3420,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134893</v>
+        <v>134134776</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>110152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,39 +3436,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716917</v>
+        <v>716866</v>
       </c>
       <c r="R28" t="n">
-        <v>6368326</v>
+        <v>6368338</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3498,11 +3498,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3511,6 +3506,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3530,7 +3530,7 @@
         <v>134134773</v>
       </c>
       <c r="B29" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,27 +3629,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134769</v>
+        <v>134134742</v>
       </c>
       <c r="B30" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3657,17 +3657,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716876</v>
+        <v>716930</v>
       </c>
       <c r="R30" t="n">
-        <v>6368320</v>
+        <v>6368372</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3731,27 +3740,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134742</v>
+        <v>134134769</v>
       </c>
       <c r="B31" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3759,26 +3768,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716930</v>
+        <v>716876</v>
       </c>
       <c r="R31" t="n">
-        <v>6368372</v>
+        <v>6368320</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134134751</v>
+        <v>134134893</v>
       </c>
       <c r="B2" t="n">
-        <v>99211</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716919</v>
+        <v>716917</v>
       </c>
       <c r="R2" t="n">
-        <v>6368337</v>
+        <v>6368326</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,6 +753,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134134729</v>
+        <v>134134894</v>
       </c>
       <c r="B3" t="n">
-        <v>110152</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716894</v>
+        <v>716908</v>
       </c>
       <c r="R3" t="n">
-        <v>6368308</v>
+        <v>6368321</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -859,6 +860,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre bohål i gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,11 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134134745</v>
+        <v>134134868</v>
       </c>
       <c r="B4" t="n">
-        <v>110152</v>
+        <v>43469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,34 +900,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>201116</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716928</v>
+        <v>716951</v>
       </c>
       <c r="R4" t="n">
-        <v>6368363</v>
+        <v>6368356</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +992,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -990,38 +1010,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134134894</v>
+        <v>134134747</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>99218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716908</v>
+        <v>716928</v>
       </c>
       <c r="R5" t="n">
-        <v>6368321</v>
+        <v>6368363</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1070,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre bohål i gran.</t>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,6 +1105,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1097,45 +1126,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134134765</v>
+        <v>134134751</v>
       </c>
       <c r="B6" t="n">
-        <v>110152</v>
+        <v>99218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716892</v>
+        <v>716919</v>
       </c>
       <c r="R6" t="n">
-        <v>6368329</v>
+        <v>6368337</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1199,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134791</v>
+        <v>134134723</v>
       </c>
       <c r="B7" t="n">
-        <v>99217</v>
+        <v>99224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,7 +1267,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1243,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716813</v>
+        <v>716841</v>
       </c>
       <c r="R7" t="n">
-        <v>6368335</v>
+        <v>6368309</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134747</v>
+        <v>134134742</v>
       </c>
       <c r="B8" t="n">
-        <v>99211</v>
+        <v>99224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1321,26 +1359,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1354,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716928</v>
+        <v>716930</v>
       </c>
       <c r="R8" t="n">
-        <v>6368363</v>
+        <v>6368372</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1390,11 +1428,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,27 +1459,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134792</v>
+        <v>134134775</v>
       </c>
       <c r="B9" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,17 +1487,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716813</v>
+        <v>716872</v>
       </c>
       <c r="R9" t="n">
-        <v>6368335</v>
+        <v>6368325</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1497,11 +1539,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>AVA slut 20 m V.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,27 +1570,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134748</v>
+        <v>134134778</v>
       </c>
       <c r="B10" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1561,17 +1598,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716919</v>
+        <v>716866</v>
       </c>
       <c r="R10" t="n">
-        <v>6368359</v>
+        <v>6368338</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1638,7 +1684,7 @@
         <v>134134780</v>
       </c>
       <c r="B11" t="n">
-        <v>99217</v>
+        <v>99224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,27 +1792,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134134789</v>
+        <v>134134791</v>
       </c>
       <c r="B12" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1774,17 +1820,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716826</v>
+        <v>716813</v>
       </c>
       <c r="R12" t="n">
-        <v>6368340</v>
+        <v>6368335</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,11 +1872,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,27 +1903,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134134755</v>
+        <v>134134794</v>
       </c>
       <c r="B13" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1881,17 +1931,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716917</v>
+        <v>716821</v>
       </c>
       <c r="R13" t="n">
-        <v>6368326</v>
+        <v>6368327</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1955,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134134743</v>
+        <v>134134727</v>
       </c>
       <c r="B14" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716930</v>
+        <v>716881</v>
       </c>
       <c r="R14" t="n">
-        <v>6368372</v>
+        <v>6368310</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134134782</v>
+        <v>134134729</v>
       </c>
       <c r="B15" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716867</v>
+        <v>716894</v>
       </c>
       <c r="R15" t="n">
-        <v>6368358</v>
+        <v>6368308</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2159,10 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134134753</v>
+        <v>134134740</v>
       </c>
       <c r="B16" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716919</v>
+        <v>716946</v>
       </c>
       <c r="R16" t="n">
-        <v>6368337</v>
+        <v>6368368</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2230,6 +2289,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>AVA gräns 10 m O.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2261,27 +2325,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134134775</v>
+        <v>134134743</v>
       </c>
       <c r="B17" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2289,26 +2353,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716872</v>
+        <v>716930</v>
       </c>
       <c r="R17" t="n">
-        <v>6368325</v>
+        <v>6368372</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2372,27 +2427,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134134778</v>
+        <v>134134745</v>
       </c>
       <c r="B18" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2400,26 +2455,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716866</v>
+        <v>716928</v>
       </c>
       <c r="R18" t="n">
-        <v>6368338</v>
+        <v>6368363</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2483,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134134767</v>
+        <v>134134748</v>
       </c>
       <c r="B19" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716880</v>
+        <v>716919</v>
       </c>
       <c r="R19" t="n">
-        <v>6368316</v>
+        <v>6368359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2585,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134134761</v>
+        <v>134134753</v>
       </c>
       <c r="B20" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716908</v>
+        <v>716919</v>
       </c>
       <c r="R20" t="n">
-        <v>6368321</v>
+        <v>6368337</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2687,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134134795</v>
+        <v>134134755</v>
       </c>
       <c r="B21" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716821</v>
+        <v>716917</v>
       </c>
       <c r="R21" t="n">
-        <v>6368327</v>
+        <v>6368326</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134134740</v>
+        <v>134134761</v>
       </c>
       <c r="B22" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716946</v>
+        <v>716908</v>
       </c>
       <c r="R22" t="n">
-        <v>6368368</v>
+        <v>6368321</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2860,11 +2906,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>AVA gräns 10 m O.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,27 +2937,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134794</v>
+        <v>134134763</v>
       </c>
       <c r="B23" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2924,26 +2965,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716821</v>
+        <v>716899</v>
       </c>
       <c r="R23" t="n">
-        <v>6368327</v>
+        <v>6368322</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134786</v>
+        <v>134134765</v>
       </c>
       <c r="B24" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3042,13 +3074,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716848</v>
+        <v>716892</v>
       </c>
       <c r="R24" t="n">
-        <v>6368363</v>
+        <v>6368329</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,11 +3112,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3096,7 +3123,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3114,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134134763</v>
+        <v>134134767</v>
       </c>
       <c r="B25" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3149,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716899</v>
+        <v>716880</v>
       </c>
       <c r="R25" t="n">
-        <v>6368322</v>
+        <v>6368316</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3216,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134893</v>
+        <v>134134769</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>110159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,39 +3254,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716917</v>
+        <v>716876</v>
       </c>
       <c r="R26" t="n">
-        <v>6368326</v>
+        <v>6368320</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3294,11 +3316,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spillkråka födosök vid basen av död gran med gott om insektshål.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3307,6 +3324,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3323,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134727</v>
+        <v>134134773</v>
       </c>
       <c r="B27" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3358,10 +3380,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716881</v>
+        <v>716872</v>
       </c>
       <c r="R27" t="n">
-        <v>6368310</v>
+        <v>6368325</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3428,7 +3450,7 @@
         <v>134134776</v>
       </c>
       <c r="B28" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134134773</v>
+        <v>134134782</v>
       </c>
       <c r="B29" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,10 +3584,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716872</v>
+        <v>716867</v>
       </c>
       <c r="R29" t="n">
-        <v>6368325</v>
+        <v>6368358</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3629,27 +3651,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134742</v>
+        <v>134134786</v>
       </c>
       <c r="B30" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3657,29 +3679,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716930</v>
+        <v>716848</v>
       </c>
       <c r="R30" t="n">
-        <v>6368372</v>
+        <v>6368363</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3711,6 +3724,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3722,7 +3740,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3740,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134769</v>
+        <v>134134789</v>
       </c>
       <c r="B31" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716876</v>
+        <v>716826</v>
       </c>
       <c r="R31" t="n">
-        <v>6368320</v>
+        <v>6368340</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3813,6 +3831,11 @@
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3839,6 +3862,322 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134134792</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>716813</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6368335</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>AVA slut 20 m V.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134134795</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>716821</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6368327</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134134781</v>
+      </c>
+      <c r="B34" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6368358</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>10 cm i diameter, kapad!</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134134868</v>
+        <v>134649358</v>
       </c>
       <c r="B4" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,53 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>201116</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716951</v>
+        <v>716991</v>
       </c>
       <c r="R4" t="n">
-        <v>6368356</v>
+        <v>6368337</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,78 +980,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134134747</v>
+        <v>134649362</v>
       </c>
       <c r="B5" t="n">
-        <v>99218</v>
+        <v>43472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716928</v>
+        <v>716963</v>
       </c>
       <c r="R5" t="n">
-        <v>6368363</v>
+        <v>6368350</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,17 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även 5 fjolårsstänglar.</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,78 +1087,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134134751</v>
+        <v>134649364</v>
       </c>
       <c r="B6" t="n">
-        <v>99218</v>
+        <v>43472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716919</v>
+        <v>716921</v>
       </c>
       <c r="R6" t="n">
-        <v>6368337</v>
+        <v>6368350</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,12 +1168,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,75 +1199,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134134723</v>
+        <v>134649367</v>
       </c>
       <c r="B7" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716841</v>
+        <v>716913</v>
       </c>
       <c r="R7" t="n">
-        <v>6368309</v>
+        <v>6368338</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,12 +1280,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,78 +1311,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134134742</v>
+        <v>134649370</v>
       </c>
       <c r="B8" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716930</v>
+        <v>716882</v>
       </c>
       <c r="R8" t="n">
-        <v>6368372</v>
+        <v>6368383</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,12 +1392,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,78 +1418,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134134775</v>
+        <v>134649372</v>
       </c>
       <c r="B9" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716872</v>
+        <v>716878</v>
       </c>
       <c r="R9" t="n">
-        <v>6368325</v>
+        <v>6368379</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,12 +1499,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,78 +1530,64 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134134778</v>
+        <v>134649374</v>
       </c>
       <c r="B10" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716866</v>
+        <v>716855</v>
       </c>
       <c r="R10" t="n">
-        <v>6368338</v>
+        <v>6368385</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,12 +1611,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>5 st förökningsyta</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,78 +1642,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134134780</v>
+        <v>134649376</v>
       </c>
       <c r="B11" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716862</v>
+        <v>716844</v>
       </c>
       <c r="R11" t="n">
-        <v>6368351</v>
+        <v>6368370</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,12 +1723,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 st, varav 2 i parning?</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,78 +1754,64 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134134791</v>
+        <v>134649378</v>
       </c>
       <c r="B12" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala Ollajvs övre, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716813</v>
+        <v>716837</v>
       </c>
       <c r="R12" t="n">
-        <v>6368335</v>
+        <v>6368407</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,12 +1835,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hotspot minst 10 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,75 +1866,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134134794</v>
+        <v>134658205</v>
       </c>
       <c r="B13" t="n">
-        <v>99224</v>
+        <v>43472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716821</v>
+        <v>716886</v>
       </c>
       <c r="R13" t="n">
-        <v>6368327</v>
+        <v>6368325</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,12 +1947,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,31 +1978,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134134727</v>
+        <v>134658208</v>
       </c>
       <c r="B14" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,34 +2005,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716881</v>
+        <v>716854</v>
       </c>
       <c r="R14" t="n">
-        <v>6368310</v>
+        <v>6368341</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2079,12 +2059,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,31 +2090,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134134729</v>
+        <v>134658213</v>
       </c>
       <c r="B15" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,34 +2117,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716894</v>
+        <v>716823</v>
       </c>
       <c r="R15" t="n">
-        <v>6368308</v>
+        <v>6368339</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2181,12 +2171,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,31 +2202,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134134740</v>
+        <v>134658216</v>
       </c>
       <c r="B16" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,34 +2229,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716946</v>
+        <v>716812</v>
       </c>
       <c r="R16" t="n">
-        <v>6368368</v>
+        <v>6368330</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2283,17 +2283,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>AVA gräns 10 m O.</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,31 +2314,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134134743</v>
+        <v>134658217</v>
       </c>
       <c r="B17" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,34 +2341,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716930</v>
+        <v>716816</v>
       </c>
       <c r="R17" t="n">
-        <v>6368372</v>
+        <v>6368325</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,12 +2395,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,31 +2426,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134134745</v>
+        <v>134658219</v>
       </c>
       <c r="B18" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,34 +2453,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716928</v>
+        <v>716797</v>
       </c>
       <c r="R18" t="n">
-        <v>6368363</v>
+        <v>6368329</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,12 +2507,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,31 +2538,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134134748</v>
+        <v>134658220</v>
       </c>
       <c r="B19" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,34 +2565,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716919</v>
+        <v>716825</v>
       </c>
       <c r="R19" t="n">
-        <v>6368359</v>
+        <v>6368358</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2594,12 +2619,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,31 +2650,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134134753</v>
+        <v>134658222</v>
       </c>
       <c r="B20" t="n">
-        <v>110159</v>
+        <v>43472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,34 +2677,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716919</v>
+        <v>716846</v>
       </c>
       <c r="R20" t="n">
-        <v>6368337</v>
+        <v>6368363</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2696,12 +2731,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,31 +2762,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134134755</v>
+        <v>134134868</v>
       </c>
       <c r="B21" t="n">
-        <v>110159</v>
+        <v>43469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,34 +2789,53 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220299</v>
+        <v>201116</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716917</v>
+        <v>716951</v>
       </c>
       <c r="R21" t="n">
-        <v>6368326</v>
+        <v>6368356</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2817,7 +2881,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2835,45 +2899,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134134761</v>
+        <v>134134747</v>
       </c>
       <c r="B22" t="n">
-        <v>110159</v>
+        <v>99218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716908</v>
+        <v>716928</v>
       </c>
       <c r="R22" t="n">
-        <v>6368321</v>
+        <v>6368363</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2906,6 +2979,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Även 5 fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,45 +3015,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134134763</v>
+        <v>134134751</v>
       </c>
       <c r="B23" t="n">
-        <v>110159</v>
+        <v>99218</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716899</v>
+        <v>716919</v>
       </c>
       <c r="R23" t="n">
-        <v>6368322</v>
+        <v>6368337</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3039,27 +3126,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134134765</v>
+        <v>134134723</v>
       </c>
       <c r="B24" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3067,17 +3154,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716892</v>
+        <v>716841</v>
       </c>
       <c r="R24" t="n">
-        <v>6368329</v>
+        <v>6368309</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3141,27 +3237,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134134767</v>
+        <v>134134742</v>
       </c>
       <c r="B25" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3169,17 +3265,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716880</v>
+        <v>716930</v>
       </c>
       <c r="R25" t="n">
-        <v>6368316</v>
+        <v>6368372</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3243,27 +3348,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134134769</v>
+        <v>134134775</v>
       </c>
       <c r="B26" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3271,17 +3376,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716876</v>
+        <v>716872</v>
       </c>
       <c r="R26" t="n">
-        <v>6368320</v>
+        <v>6368325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3345,27 +3459,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134134773</v>
+        <v>134134778</v>
       </c>
       <c r="B27" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3373,17 +3487,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716872</v>
+        <v>716866</v>
       </c>
       <c r="R27" t="n">
-        <v>6368325</v>
+        <v>6368338</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3447,27 +3570,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134134776</v>
+        <v>134134780</v>
       </c>
       <c r="B28" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3475,17 +3598,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716866</v>
+        <v>716862</v>
       </c>
       <c r="R28" t="n">
-        <v>6368338</v>
+        <v>6368351</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3549,27 +3681,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134134782</v>
+        <v>134134791</v>
       </c>
       <c r="B29" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3577,17 +3709,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716867</v>
+        <v>716813</v>
       </c>
       <c r="R29" t="n">
-        <v>6368358</v>
+        <v>6368335</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3651,27 +3792,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134134786</v>
+        <v>134134794</v>
       </c>
       <c r="B30" t="n">
-        <v>110159</v>
+        <v>99224</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3679,20 +3820,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716848</v>
+        <v>716821</v>
       </c>
       <c r="R30" t="n">
-        <v>6368363</v>
+        <v>6368327</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3724,11 +3874,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridd. 40 m S skiftesgräns.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3740,7 +3885,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3758,7 +3903,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134134789</v>
+        <v>134134727</v>
       </c>
       <c r="B31" t="n">
         <v>110159</v>
@@ -3793,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716826</v>
+        <v>716881</v>
       </c>
       <c r="R31" t="n">
-        <v>6368340</v>
+        <v>6368310</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3829,11 +3974,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,7 +4005,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134134792</v>
+        <v>134134729</v>
       </c>
       <c r="B32" t="n">
         <v>110159</v>
@@ -3900,10 +4040,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716813</v>
+        <v>716894</v>
       </c>
       <c r="R32" t="n">
-        <v>6368335</v>
+        <v>6368308</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3936,11 +4076,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>AVA slut 20 m V.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,7 +4107,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134134795</v>
+        <v>134134740</v>
       </c>
       <c r="B33" t="n">
         <v>110159</v>
@@ -4007,10 +4142,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716821</v>
+        <v>716946</v>
       </c>
       <c r="R33" t="n">
-        <v>6368327</v>
+        <v>6368368</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4043,6 +4178,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>AVA gräns 10 m O.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,27 +4214,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134134781</v>
+        <v>134134743</v>
       </c>
       <c r="B34" t="n">
-        <v>103907</v>
+        <v>110159</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223284</v>
+        <v>220299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4109,10 +4249,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716867</v>
+        <v>716930</v>
       </c>
       <c r="R34" t="n">
-        <v>6368358</v>
+        <v>6368372</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4147,11 +4287,6 @@
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>10 cm i diameter, kapad!</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4178,6 +4313,1760 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134134745</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>716928</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6368363</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134134748</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>716919</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6368359</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134134753</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>716919</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6368337</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134134755</v>
+      </c>
+      <c r="B38" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>716917</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6368326</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134134761</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>716908</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6368321</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134134763</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>716899</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6368322</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134134765</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>716892</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6368329</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134134767</v>
+      </c>
+      <c r="B42" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6368316</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134134769</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>716876</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6368320</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134134773</v>
+      </c>
+      <c r="B44" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>716872</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6368325</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134134776</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>716866</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6368338</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134134782</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6368358</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134134786</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>716848</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6368363</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spridd. 40 m S skiftesgräns.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog blåtåtelfuktmark, röjd.</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134134789</v>
+      </c>
+      <c r="B48" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>716826</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6368340</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134134792</v>
+      </c>
+      <c r="B49" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>716813</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6368335</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>AVA slut 20 m V.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134134795</v>
+      </c>
+      <c r="B50" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>716821</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6368327</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134134781</v>
+      </c>
+      <c r="B51" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 N-del, A 63152-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6368358</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>10 cm i diameter, kapad!</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog nedom kalksluttning mot fuktigare mark med blåtåtel. Röjd på buskar och mindre träd inför avverkning.-</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -1982,12 +1982,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2094,12 +2094,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2206,12 +2206,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2318,12 +2318,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2430,12 +2430,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2542,12 +2542,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2654,12 +2654,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2766,12 +2766,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 63152-2025 artfynd.xlsx
+++ b/artfynd/A 63152-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649358</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649362</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649364</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649367</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649370</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649372</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649376</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649378</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1991,6 +2051,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658205</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658208</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2215,6 +2285,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658213</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658216</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2439,6 +2519,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658217</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658219</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658220</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2775,6 +2870,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658222</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2896,6 +2996,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134868</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3012,6 +3117,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3233,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134751</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3234,6 +3349,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134723</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3345,6 +3465,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134742</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3456,6 +3581,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134775</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3567,6 +3697,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134778</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3678,6 +3813,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134780</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3789,6 +3929,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134791</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3900,6 +4045,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134794</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4002,6 +4152,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134727</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4104,6 +4259,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134729</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4211,6 +4371,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134740</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4313,6 +4478,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134743</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4415,6 +4585,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134745</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4517,6 +4692,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134748</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4619,6 +4799,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134753</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4721,6 +4906,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134755</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4823,6 +5013,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134761</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4925,6 +5120,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134763</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5027,6 +5227,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134765</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5129,6 +5334,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134767</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5231,6 +5441,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134769</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5333,6 +5548,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134773</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5435,6 +5655,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134776</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5537,6 +5762,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134782</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5644,6 +5874,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134786</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5751,6 +5986,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134789</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5858,6 +6098,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134792</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5960,6 +6205,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134795</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6067,8 +6317,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>